--- a/DateBase/orders/Nhat 48_2026-3-12.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-12.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -777,10 +777,96 @@
       <c r="A41" t="str">
         <v>6</v>
       </c>
+      <c r="C41" t="str">
+        <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F41" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>648_洋牡丹河内_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>551_铁线莲_Glematis_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>790_铁线莲粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F46" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>7</v>
+      </c>
+      <c r="C47" t="str">
+        <v>586_洋牡丹白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>590_洋牡丹粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>840_洋牡丹塞纳河_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>774_紫娇花_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>878_玛格丽特粉_undefined_undefined_1bunch</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -835,7 +921,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0805030301515555510510105205154015151010510115810915751583020200</v>
+        <v>080503030151555551051010520515401515101051011581091575158302020201015105520201050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-12.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-12.xlsx
@@ -863,6 +863,9 @@
       <c r="C51" t="str">
         <v>878_玛格丽特粉_undefined_undefined_1bunch</v>
       </c>
+      <c r="F51" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -921,7 +924,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>080503030151555551051010520515401515101051011581091575158302020201015105520201050</v>
+        <v>080503030151555551051010520515401515101051011581091575158302020201015105520201051</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-12.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-12.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L58"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -864,12 +864,75 @@
         <v>878_玛格丽特粉_undefined_undefined_1bunch</v>
       </c>
       <c r="F51" t="str">
-        <v>1</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" xml:space="preserve">
+      <c r="A52" t="str">
+        <v>8</v>
+      </c>
+      <c r="C52" t="str" xml:space="preserve">
+        <v xml:space="preserve">373_龙柳_Salix
+_undefined_1bunch</v>
+      </c>
+      <c r="F52" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>10</v>
+      </c>
+      <c r="C53" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F53" t="str">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>757_芍药老忠诚_Old Faith_undefined_10stems</v>
+      </c>
+      <c r="F54" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>759_芍药红富士_Kansas_undefined_10stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>761_芍药奶油碗_undefined_undefined_10stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>745_海芋红_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F57" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>547_粉菠萝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F58" t="str">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L58"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -924,7 +987,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>080503030151555551051010520515401515101051011581091575158302020201015105520201051</v>
+        <v>08050303015155555105101052051540151510105101158109157515830202020101510552020105151580503050210</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-12.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-12.xlsx
@@ -989,6 +989,9 @@
       <c r="G2" t="str">
         <v>08050303015155555105101052051540151510105101158109157515830202020101510552020105151580503050210</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
